--- a/doanmon/FILE_2_CAP_NHAT_SO_LUONG.xlsx
+++ b/doanmon/FILE_2_CAP_NHAT_SO_LUONG.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>productCode</t>
   </si>
@@ -32,58 +32,61 @@
     <t>description</t>
   </si>
   <si>
-    <t>CAKE-CHOCO-001</t>
-  </si>
-  <si>
-    <t>Chocolate Fudge Cake</t>
-  </si>
-  <si>
-    <t>Chocolate</t>
-  </si>
-  <si>
-    <t>Restocking chocolate fudge</t>
-  </si>
-  <si>
-    <t>CAKE-CHOCO-002</t>
-  </si>
-  <si>
-    <t>Chocolate Truffle Delight</t>
-  </si>
-  <si>
-    <t>Restocking truffle cake</t>
-  </si>
-  <si>
-    <t>CAKE-VANILLA-001</t>
-  </si>
-  <si>
-    <t>Classic Vanilla Sponge</t>
-  </si>
-  <si>
-    <t>Vanilla</t>
-  </si>
-  <si>
-    <t>Restocking vanilla sponge</t>
-  </si>
-  <si>
-    <t>CAKE-FRUIT-001</t>
-  </si>
-  <si>
-    <t>Strawberry Shortcake</t>
-  </si>
-  <si>
-    <t>Fruit</t>
-  </si>
-  <si>
-    <t>Restocking strawberry cake</t>
-  </si>
-  <si>
-    <t>CAKE-SPECIAL-001</t>
-  </si>
-  <si>
-    <t>Red Velvet Classic</t>
-  </si>
-  <si>
-    <t>Restocking red velvet</t>
+    <t>CAKE-BDAY-001</t>
+  </si>
+  <si>
+    <t>Rainbow Birthday Cake</t>
+  </si>
+  <si>
+    <t>Birthday Cakes</t>
+  </si>
+  <si>
+    <t>Restocking birthday cakes</t>
+  </si>
+  <si>
+    <t>CAKE-BDAY-002</t>
+  </si>
+  <si>
+    <t>Unicorn Dream Cake</t>
+  </si>
+  <si>
+    <t>Restocking unicorn cakes</t>
+  </si>
+  <si>
+    <t>CAKE-WEDDING-001</t>
+  </si>
+  <si>
+    <t>Classic White Wedding Cake</t>
+  </si>
+  <si>
+    <t>Wedding Cakes</t>
+  </si>
+  <si>
+    <t>Restocking wedding cakes</t>
+  </si>
+  <si>
+    <t>CAKE-CHEESE-001</t>
+  </si>
+  <si>
+    <t>New York Cheesecake</t>
+  </si>
+  <si>
+    <t>Cheese Cakes</t>
+  </si>
+  <si>
+    <t>Restocking cheesecakes</t>
+  </si>
+  <si>
+    <t>CAKE-GATAUX-001</t>
+  </si>
+  <si>
+    <t>Black Forest Gataux</t>
+  </si>
+  <si>
+    <t>Gataux</t>
+  </si>
+  <si>
+    <t>Restocking gataux</t>
   </si>
 </sst>
 </file>
@@ -147,12 +150,12 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="20.203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="17.15234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="22.390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="5.46875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="13.75" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="8.44140625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="22.08203125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="21.12109375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -183,7 +186,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>28.99</v>
+        <v>35.99</v>
       </c>
       <c r="D2" t="s" s="0">
         <v>8</v>
@@ -203,7 +206,7 @@
         <v>11</v>
       </c>
       <c r="C3" t="n" s="0">
-        <v>32.5</v>
+        <v>42.5</v>
       </c>
       <c r="D3" t="s" s="0">
         <v>8</v>
@@ -223,13 +226,13 @@
         <v>14</v>
       </c>
       <c r="C4" t="n" s="0">
-        <v>18.99</v>
+        <v>150.0</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>15</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>30.0</v>
+        <v>5.0</v>
       </c>
       <c r="F4" t="s" s="0">
         <v>16</v>
@@ -243,7 +246,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>24.99</v>
+        <v>28.99</v>
       </c>
       <c r="D5" t="s" s="0">
         <v>19</v>
@@ -263,16 +266,16 @@
         <v>22</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>29.99</v>
+        <v>45.99</v>
       </c>
       <c r="D6" t="s" s="0">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n" s="0">
         <v>10.0</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
